--- a/generator/data/kek/kek_adjectives.xlsx
+++ b/generator/data/kek/kek_adjectives.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc6ec0edc09a2fcc/Documents/GitHub/kek-sentence-generator/data/kek/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="898" documentId="8_{D1AFB617-EB40-4399-BDD5-E81CB7BB894F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BBA9E1C-CAC0-4F4E-A7E4-924EDEB11B2D}"/>
+  <xr:revisionPtr revIDLastSave="1027" documentId="8_{D1AFB617-EB40-4399-BDD5-E81CB7BB894F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{507B1294-3C6B-4216-9FDF-D0177D7B4349}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{6F197F4E-509E-4648-9E41-15D7F5089760}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">semantics_adjectives!$A$1:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">semantics_adjectives!$A$1:$K$150</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="550">
   <si>
     <t>lemma_kek</t>
   </si>
@@ -858,9 +858,6 @@
     <t>human;kinship</t>
   </si>
   <si>
-    <t>fruit</t>
-  </si>
-  <si>
     <t>food</t>
   </si>
   <si>
@@ -1308,9 +1305,6 @@
     <t>artifact;boy_part;clothing;tool;vehicle</t>
   </si>
   <si>
-    <t>place</t>
-  </si>
-  <si>
     <t>vehicle</t>
   </si>
   <si>
@@ -1560,13 +1554,142 @@
     <t>p_debug_percent</t>
   </si>
   <si>
-    <t>nicer</t>
-  </si>
-  <si>
     <t>wiser</t>
   </si>
   <si>
     <t>whiter</t>
+  </si>
+  <si>
+    <t>lujuch</t>
+  </si>
+  <si>
+    <t>taller</t>
+  </si>
+  <si>
+    <t>meqes</t>
+  </si>
+  <si>
+    <t>pelek</t>
+  </si>
+  <si>
+    <t>skinny</t>
+  </si>
+  <si>
+    <t>delgado</t>
+  </si>
+  <si>
+    <t>teb'es</t>
+  </si>
+  <si>
+    <t>chubbier</t>
+  </si>
+  <si>
+    <t>fat/chubby</t>
+  </si>
+  <si>
+    <t>stiffer</t>
+  </si>
+  <si>
+    <t>q'eenak</t>
+  </si>
+  <si>
+    <t>surso</t>
+  </si>
+  <si>
+    <t>circular</t>
+  </si>
+  <si>
+    <t>more circular</t>
+  </si>
+  <si>
+    <t>artifact;building;tool</t>
+  </si>
+  <si>
+    <t>xab'etal</t>
+  </si>
+  <si>
+    <t>uglier</t>
+  </si>
+  <si>
+    <t>human;kinship;occupation;animal_domesticated;animal_wild;artifact;tool</t>
+  </si>
+  <si>
+    <t>xomxo</t>
+  </si>
+  <si>
+    <t>dented</t>
+  </si>
+  <si>
+    <t>abollado</t>
+  </si>
+  <si>
+    <t>artifact;tool;vehicle</t>
+  </si>
+  <si>
+    <t>xujxuj</t>
+  </si>
+  <si>
+    <t>fragile</t>
+  </si>
+  <si>
+    <t>more fragile</t>
+  </si>
+  <si>
+    <t>frágil</t>
+  </si>
+  <si>
+    <t>yach</t>
+  </si>
+  <si>
+    <t>naked</t>
+  </si>
+  <si>
+    <t>more naked</t>
+  </si>
+  <si>
+    <t>desnudo</t>
+  </si>
+  <si>
+    <t>sak'a</t>
+  </si>
+  <si>
+    <t>diligent</t>
+  </si>
+  <si>
+    <t>more diligent</t>
+  </si>
+  <si>
+    <t>diligente</t>
+  </si>
+  <si>
+    <t>animal_domestic;animal_wild;artifact;body_part;building;fruit;food;insect;tool;vegetable</t>
+  </si>
+  <si>
+    <t>human;kinship;occupation;animal_domesticated;animal_wild;insect</t>
+  </si>
+  <si>
+    <t>building;container;place</t>
+  </si>
+  <si>
+    <t>funny</t>
+  </si>
+  <si>
+    <t>humorístico</t>
+  </si>
+  <si>
+    <t>se'se' ru</t>
+  </si>
+  <si>
+    <t>obese</t>
+  </si>
+  <si>
+    <t>more obese</t>
+  </si>
+  <si>
+    <t>obeso</t>
+  </si>
+  <si>
+    <t>t'inis</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1832,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1889,6 +2012,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2050,7 +2179,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2062,7 +2191,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4189,7 +4319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11844E47-879C-4E47-A038-CD7309E4AAED}">
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.265625" customWidth="1"/>
@@ -4198,7 +4328,7 @@
     <col min="4" max="4" width="15.73046875" customWidth="1"/>
     <col min="6" max="6" width="15.73046875" customWidth="1"/>
     <col min="7" max="7" width="37.53125" customWidth="1"/>
-    <col min="8" max="8" width="45.9296875" customWidth="1"/>
+    <col min="8" max="8" width="71.6640625" customWidth="1"/>
     <col min="9" max="9" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4210,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>265</v>
       </c>
       <c r="E1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F1" t="s">
         <v>269</v>
@@ -4225,33 +4355,33 @@
         <v>270</v>
       </c>
       <c r="H1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>135</v>
@@ -4274,22 +4404,22 @@
         <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>211</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J3" s="5">
         <v>83176.377110267</v>
@@ -4306,13 +4436,13 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F4" t="s">
         <v>83</v>
@@ -4321,7 +4451,7 @@
         <v>271</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J4" s="5">
         <v>26302.6799189538</v>
@@ -4332,31 +4462,31 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J5" s="5">
         <v>21379.620895022301</v>
@@ -4367,25 +4497,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J6" s="5">
         <v>58884.365535558798</v>
@@ -4406,16 +4536,16 @@
         <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J7" s="5">
         <v>45708.818961487501</v>
@@ -4432,22 +4562,22 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J8" s="5">
         <v>13489.628825916499</v>
@@ -4458,28 +4588,28 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J9" s="5">
         <v>5495.4087385762396</v>
@@ -4500,7 +4630,7 @@
         <v>261</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F10" t="s">
         <v>107</v>
@@ -4523,19 +4653,19 @@
         <v>130</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>193</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F11" t="s">
         <v>107</v>
       </c>
       <c r="G11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J11" s="5">
         <v>165958.690743755</v>
@@ -4556,16 +4686,16 @@
         <v>220</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F12" t="s">
         <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I12" t="s">
         <v>146</v>
@@ -4585,22 +4715,22 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>202</v>
       </c>
       <c r="E13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J13" s="5">
         <v>16218.1009735892</v>
@@ -4621,13 +4751,13 @@
         <v>229</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
@@ -4651,13 +4781,13 @@
         <v>238</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
@@ -4681,7 +4811,7 @@
         <v>222</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F16" t="s">
         <v>87</v>
@@ -4704,22 +4834,22 @@
         <v>108</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J17" s="5">
         <v>75857.757502918306</v>
@@ -4730,28 +4860,28 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J18" s="5">
         <v>75857.757502918306</v>
@@ -4772,13 +4902,13 @@
         <v>227</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -4792,23 +4922,23 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E20" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F20" t="s">
         <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J20" s="5">
         <v>602.55958607435696</v>
@@ -4819,23 +4949,23 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H21" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J21" s="5">
         <v>1995.26231496887</v>
@@ -4856,16 +4986,16 @@
         <v>262</v>
       </c>
       <c r="E22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J22" s="5">
         <v>40738.027780411299</v>
@@ -4876,7 +5006,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>111</v>
@@ -4886,19 +5016,19 @@
         <v>262</v>
       </c>
       <c r="E23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J23" s="5">
         <v>40738.027780411299</v>
@@ -4919,16 +5049,16 @@
         <v>212</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F24" t="s">
         <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J24" s="5">
         <v>51286.138399136398</v>
@@ -4945,22 +5075,22 @@
         <v>139</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>240</v>
       </c>
       <c r="E25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J25" s="5">
         <v>18197.008586099801</v>
@@ -4981,16 +5111,16 @@
         <v>223</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H26" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J26" s="5">
         <v>2691.5348039269102</v>
@@ -5001,23 +5131,23 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J27" s="5">
         <v>2691.5348039269102</v>
@@ -5028,3237 +5158,3556 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>513</v>
+      </c>
       <c r="D28" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E28" t="s">
-        <v>416</v>
-      </c>
-      <c r="F28" t="s">
-        <v>29</v>
+        <v>398</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>421</v>
-      </c>
-      <c r="J28" s="5">
-        <v>93325.430079698999</v>
-      </c>
-      <c r="K28" s="5">
-        <v>0.82556308658649502</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>517</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="1"/>
+        <v>518</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>519</v>
+      </c>
       <c r="D29" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" t="s">
-        <v>416</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>273</v>
-      </c>
-      <c r="J29" s="5">
-        <v>104712.85480508899</v>
-      </c>
-      <c r="K29" s="5">
-        <v>0.92629701834053702</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>353</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>462</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>393</v>
+        <v>249</v>
       </c>
       <c r="E30" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F30" t="s">
-        <v>437</v>
-      </c>
-      <c r="H30" t="s">
-        <v>414</v>
+        <v>29</v>
+      </c>
+      <c r="G30" t="s">
+        <v>420</v>
       </c>
       <c r="J30" s="5">
-        <v>125892.541179416</v>
+        <v>93325.430079698999</v>
       </c>
       <c r="K30" s="5">
-        <v>1.1136539610429801</v>
+        <v>0.82556308658649502</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>463</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F31" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>442</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J31">
-        <v>100000</v>
+        <v>272</v>
+      </c>
+      <c r="J31" s="5">
+        <v>104712.85480508899</v>
       </c>
       <c r="K31" s="5">
-        <v>0.88460678496897605</v>
+        <v>0.92629701834053702</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>352</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>460</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E32" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" t="s">
         <v>415</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="H32" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J32" s="5">
-        <v>24547.089156850201</v>
+        <v>125892.541179416</v>
       </c>
       <c r="K32" s="5">
-        <v>0.217145216193881</v>
+        <v>1.1136539610429801</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="E33" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>430</v>
-      </c>
-      <c r="H33" t="s">
-        <v>411</v>
-      </c>
-      <c r="J33" s="5">
-        <v>9772.3722095581106</v>
-      </c>
-      <c r="K33">
-        <v>8.6447067618173695E-2</v>
+        <v>440</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J33">
+        <v>100000</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.88460678496897605</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" t="s">
-        <v>416</v>
+        <v>256</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>431</v>
+        <v>419</v>
+      </c>
+      <c r="H34" t="s">
+        <v>413</v>
       </c>
       <c r="J34" s="5">
-        <v>5011.8723362727196</v>
+        <v>24547.089156850201</v>
       </c>
       <c r="K34" s="5">
-        <v>4.4335362740651599E-2</v>
+        <v>0.217145216193881</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>335</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C35" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>462</v>
+      </c>
       <c r="D35" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" t="s">
         <v>415</v>
       </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
       <c r="G35" t="s">
-        <v>442</v>
-      </c>
-      <c r="J35">
-        <v>8317.6377110267094</v>
+        <v>428</v>
+      </c>
+      <c r="H35" t="s">
+        <v>410</v>
+      </c>
+      <c r="J35" s="5">
+        <v>9772.3722095581106</v>
       </c>
       <c r="K35">
-        <v>7.3578387540880502E-2</v>
+        <v>8.6447067618173695E-2</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>334</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>151</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" t="s">
         <v>415</v>
       </c>
+      <c r="F36" t="s">
+        <v>80</v>
+      </c>
       <c r="G36" t="s">
-        <v>497</v>
+        <v>429</v>
       </c>
       <c r="J36" s="5">
-        <v>9772.3722095581106</v>
-      </c>
-      <c r="K36">
-        <v>8.6447067618173695E-2</v>
+        <v>5011.8723362727196</v>
+      </c>
+      <c r="K36" s="5">
+        <v>4.4335362740651599E-2</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
+        <v>334</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E37" t="s">
-        <v>415</v>
-      </c>
-      <c r="F37" t="s">
-        <v>83</v>
+        <v>385</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G37" t="s">
-        <v>497</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J37" s="5">
-        <v>9772.3722095581106</v>
+        <v>440</v>
+      </c>
+      <c r="J37">
+        <v>8317.6377110267094</v>
       </c>
       <c r="K37">
-        <v>8.6447067618173695E-2</v>
+        <v>7.3578387540880502E-2</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>465</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" t="s">
-        <v>416</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
+        <v>263</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G38" t="s">
-        <v>431</v>
-      </c>
-      <c r="H38" t="s">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="J38" s="5">
-        <v>21877.616239495499</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0.193530877644051</v>
+        <v>9772.3722095581106</v>
+      </c>
+      <c r="K38">
+        <v>8.6447067618173695E-2</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>299</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>466</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>402</v>
+        <v>263</v>
       </c>
       <c r="E39" t="s">
-        <v>416</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>414</v>
+      </c>
+      <c r="F39" t="s">
+        <v>83</v>
       </c>
       <c r="G39" t="s">
-        <v>271</v>
+        <v>495</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>300</v>
+        <v>434</v>
       </c>
       <c r="J39" s="5">
-        <v>13803.842646028799</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0.122109728633212</v>
+        <v>9772.3722095581106</v>
+      </c>
+      <c r="K39">
+        <v>8.6447067618173695E-2</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>309</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>310</v>
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
         <v>415</v>
       </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>429</v>
+      </c>
+      <c r="H40" t="s">
+        <v>426</v>
+      </c>
       <c r="J40" s="5">
-        <v>173780.08287493701</v>
+        <v>21877.616239495499</v>
       </c>
       <c r="K40" s="5">
-        <v>1.5372704040364</v>
+        <v>0.193530877644051</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="1"/>
+        <v>524</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>525</v>
+      </c>
       <c r="D41" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E41" t="s">
-        <v>416</v>
-      </c>
-      <c r="F41" t="s">
-        <v>29</v>
-      </c>
-      <c r="G41" t="s">
-        <v>421</v>
-      </c>
-      <c r="J41" s="5">
-        <v>35481.3389233575</v>
-      </c>
-      <c r="K41">
-        <v>0.31387033151385901</v>
+        <v>526</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>152</v>
-      </c>
-      <c r="B42" t="s">
-        <v>120</v>
+        <v>298</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E42" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E42" t="s">
         <v>415</v>
       </c>
-      <c r="F42" t="s">
-        <v>50</v>
+      <c r="F42" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="G42" t="s">
-        <v>442</v>
+        <v>271</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="J42" s="5">
-        <v>3311.3112148259102</v>
+        <v>13803.842646028799</v>
       </c>
       <c r="K42" s="5">
-        <v>2.92920836777886E-2</v>
+        <v>0.122109728633212</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>153</v>
-      </c>
-      <c r="B43" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>308</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="D43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E43" t="s">
-        <v>416</v>
-      </c>
-      <c r="F43" t="s">
-        <v>132</v>
-      </c>
-      <c r="G43" t="s">
-        <v>422</v>
-      </c>
-      <c r="H43" t="s">
+        <v>373</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>414</v>
       </c>
       <c r="J43" s="5">
-        <v>38904.514499427998</v>
+        <v>173780.08287493701</v>
       </c>
       <c r="K43" s="5">
-        <v>0.34415197492117899</v>
+        <v>1.5372704040364</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>536</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>537</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F44" t="s">
-        <v>50</v>
+        <v>539</v>
+      </c>
+      <c r="E44" t="s">
+        <v>414</v>
       </c>
       <c r="G44" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J44" s="5">
-        <v>107151.93052376001</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0.94787324763842995</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>470</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E45" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
         <v>415</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G45" t="s">
         <v>420</v>
       </c>
-      <c r="H45" t="s">
-        <v>414</v>
-      </c>
       <c r="J45" s="5">
-        <v>48977.881936844598</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0.433261666747422</v>
+        <v>35481.3389233575</v>
+      </c>
+      <c r="K45">
+        <v>0.31387033151385901</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>332</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>333</v>
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E46" t="s">
-        <v>416</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>185</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F46" t="s">
+        <v>50</v>
       </c>
       <c r="G46" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J46" s="5">
-        <v>61659.500186148201</v>
+        <v>3311.3112148259102</v>
       </c>
       <c r="K46" s="5">
-        <v>0.54544412222462502</v>
+        <v>2.92920836777886E-2</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>314</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>315</v>
+        <v>153</v>
+      </c>
+      <c r="B47" t="s">
+        <v>133</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E47" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E47" t="s">
         <v>415</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>424</v>
+      <c r="F47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G47" t="s">
+        <v>542</v>
       </c>
       <c r="H47" t="s">
-        <v>5</v>
+        <v>413</v>
       </c>
       <c r="J47" s="5">
-        <v>323593.65692962799</v>
+        <v>38904.514499427998</v>
       </c>
       <c r="K47" s="5">
-        <v>2.8625314449287198</v>
+        <v>0.34415197492117899</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>102</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>467</v>
+      </c>
       <c r="D48" s="1" t="s">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>423</v>
+        <v>440</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J48" s="5">
-        <v>134896.28825916501</v>
+        <v>107151.93052376001</v>
       </c>
       <c r="K48" s="5">
-        <v>1.1933017186118799</v>
+        <v>0.94787324763842995</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>297</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>468</v>
+      </c>
       <c r="D49" s="1" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>443</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>370</v>
+        <v>419</v>
+      </c>
+      <c r="H49" t="s">
+        <v>413</v>
       </c>
       <c r="J49" s="5">
-        <v>70794.578438413693</v>
+        <v>48977.881936844598</v>
       </c>
       <c r="K49" s="5">
-        <v>0.62625364425639096</v>
+        <v>0.433261666747422</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C50" s="1"/>
+        <v>332</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="D50" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E50" t="s">
         <v>415</v>
       </c>
+      <c r="F50" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="G50" t="s">
-        <v>443</v>
+        <v>440</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J50" s="5">
-        <v>70794.578438413693</v>
+        <v>61659.500186148201</v>
       </c>
       <c r="K50" s="5">
-        <v>0.62625364425639096</v>
+        <v>0.54544412222462502</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>471</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E51" t="s">
-        <v>416</v>
-      </c>
-      <c r="G51" t="s">
-        <v>272</v>
+        <v>375</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="H51" t="s">
-        <v>414</v>
+        <v>5</v>
       </c>
       <c r="J51" s="5">
-        <v>1513.5612484362</v>
+        <v>323593.65692962799</v>
       </c>
       <c r="K51" s="5">
-        <v>1.33890654983278E-2</v>
+        <v>2.8625314449287198</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>352</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E52" t="s">
-        <v>416</v>
+        <v>250</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F52" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="J52" s="5">
-        <v>12589.2541179416</v>
+        <v>134896.28825916501</v>
       </c>
       <c r="K52" s="5">
-        <v>0.11136539610429801</v>
+        <v>1.1933017186118799</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" t="s">
-        <v>42</v>
+        <v>296</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E53" t="s">
-        <v>416</v>
-      </c>
-      <c r="F53" t="s">
-        <v>29</v>
+        <v>398</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G53" t="s">
-        <v>413</v>
-      </c>
-      <c r="J53">
-        <v>6309.5734448019302</v>
+        <v>441</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="J53" s="5">
+        <v>70794.578438413693</v>
       </c>
       <c r="K53" s="5">
-        <v>5.5814914795318603E-2</v>
+        <v>0.62625364425639096</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" t="s">
-        <v>126</v>
+        <v>325</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F54" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" t="s">
-        <v>498</v>
+        <v>414</v>
+      </c>
+      <c r="G54" t="s">
+        <v>441</v>
       </c>
       <c r="J54" s="5">
-        <v>52480.746024977198</v>
+        <v>70794.578438413693</v>
       </c>
       <c r="K54" s="5">
-        <v>0.46424824013928401</v>
+        <v>0.62625364425639096</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>157</v>
-      </c>
-      <c r="B55" t="s">
-        <v>137</v>
+        <v>336</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E55" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E55" t="s">
         <v>415</v>
       </c>
-      <c r="F55" t="s">
-        <v>95</v>
-      </c>
       <c r="G55" t="s">
-        <v>271</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
+      </c>
+      <c r="H55" t="s">
+        <v>413</v>
       </c>
       <c r="J55" s="5">
-        <v>24547.089156850201</v>
+        <v>1513.5612484362</v>
       </c>
       <c r="K55" s="5">
-        <v>0.217145216193881</v>
+        <v>1.33890654983278E-2</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>158</v>
-      </c>
-      <c r="B56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>473</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F56" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G56" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="J56" s="5">
-        <v>67608.297539198102</v>
+        <v>12589.2541179416</v>
       </c>
       <c r="K56" s="5">
-        <v>0.59806758723375997</v>
+        <v>0.11136539610429801</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="E57" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F57" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="G57" t="s">
-        <v>422</v>
-      </c>
-      <c r="J57" s="5">
-        <v>346736.85045253101</v>
+        <v>412</v>
+      </c>
+      <c r="J57">
+        <v>6309.5734448019302</v>
       </c>
       <c r="K57" s="5">
-        <v>3.0672577050908201</v>
+        <v>5.5814914795318603E-2</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>306</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>307</v>
+        <v>156</v>
+      </c>
+      <c r="B58" t="s">
+        <v>126</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>373</v>
+        <v>254</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
+      </c>
+      <c r="F58" t="s">
+        <v>26</v>
       </c>
       <c r="H58" t="s">
-        <v>5</v>
+        <v>496</v>
       </c>
       <c r="J58" s="5">
-        <v>46773.514128719798</v>
+        <v>52480.746024977198</v>
       </c>
       <c r="K58" s="5">
-        <v>0.41376167955107801</v>
+        <v>0.46424824013928401</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>470</v>
+      </c>
       <c r="D59" s="1" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="H59" t="s">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="G59" t="s">
+        <v>271</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J59" s="5">
-        <v>134896.28825916501</v>
+        <v>24547.089156850201</v>
       </c>
       <c r="K59" s="5">
-        <v>1.1933017186118799</v>
+        <v>0.217145216193881</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>45</v>
+      <c r="A60" s="6" t="s">
+        <v>508</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>470</v>
+      </c>
       <c r="D60" s="1" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H60" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" s="5">
-        <v>30199.5172040201</v>
-      </c>
-      <c r="K60" s="5">
-        <v>0.26714697821463501</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G60" t="s">
+        <v>271</v>
+      </c>
+      <c r="H60" s="1"/>
+      <c r="J60" s="5"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>528</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C61" t="s">
+        <v>530</v>
+      </c>
       <c r="D61" s="1" t="s">
-        <v>201</v>
+        <v>531</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G61" t="s">
-        <v>442</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J61" s="5">
-        <v>2951.2092266663799</v>
-      </c>
-      <c r="K61" s="5">
-        <v>2.6106597057721299E-2</v>
+        <v>107</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>318</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C62" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="B62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>471</v>
+      </c>
       <c r="D62" s="1" t="s">
-        <v>378</v>
+        <v>190</v>
       </c>
       <c r="E62" t="s">
-        <v>416</v>
+        <v>415</v>
+      </c>
+      <c r="F62" t="s">
+        <v>80</v>
       </c>
       <c r="G62" t="s">
-        <v>271</v>
+        <v>430</v>
       </c>
       <c r="J62" s="5">
-        <v>40738.027780411299</v>
+        <v>67608.297539198102</v>
       </c>
       <c r="K62" s="5">
-        <v>0.36037135780806401</v>
+        <v>0.59806758723375997</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="E63" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F63" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="G63" t="s">
-        <v>271</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>436</v>
+        <v>542</v>
       </c>
       <c r="J63" s="5">
-        <v>223872.11385683299</v>
+        <v>346736.85045253101</v>
       </c>
       <c r="K63" s="5">
-        <v>1.9803879088310199</v>
+        <v>3.0672577050908201</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>160</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>543</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E64" t="s">
-        <v>416</v>
-      </c>
-      <c r="F64" t="s">
-        <v>105</v>
+        <v>544</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="G64" t="s">
-        <v>433</v>
-      </c>
-      <c r="J64" s="5">
-        <v>338844.15613920201</v>
-      </c>
-      <c r="K64" s="5">
-        <v>2.99743839567825</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>218</v>
+        <v>372</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G65" t="s">
-        <v>271</v>
+        <v>414</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H65" t="s">
+        <v>5</v>
       </c>
       <c r="J65" s="5">
-        <v>13803.842646028799</v>
+        <v>46773.514128719798</v>
       </c>
       <c r="K65" s="5">
-        <v>0.122109728633212</v>
+        <v>0.41376167955107801</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F66" t="s">
-        <v>92</v>
-      </c>
-      <c r="G66" t="s">
-        <v>430</v>
+        <v>16</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H66" t="s">
+        <v>5</v>
       </c>
       <c r="J66" s="5">
-        <v>91201.083935590897</v>
+        <v>134896.28825916501</v>
       </c>
       <c r="K66" s="5">
-        <v>0.80677097645948803</v>
+        <v>1.1933017186118799</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>162</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>474</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F67" t="s">
-        <v>50</v>
-      </c>
-      <c r="G67" t="s">
-        <v>442</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>436</v>
+        <v>16</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H67" t="s">
+        <v>5</v>
       </c>
       <c r="J67" s="5">
-        <v>53703.1796370253</v>
+        <v>30199.5172040201</v>
       </c>
       <c r="K67" s="5">
-        <v>0.47506197081320301</v>
+        <v>0.26714697821463501</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E68" t="s">
-        <v>416</v>
-      </c>
-      <c r="F68" t="s">
-        <v>32</v>
+        <v>201</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="G68" t="s">
-        <v>273</v>
+        <v>440</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J68" s="5">
-        <v>144543.977074592</v>
+        <v>2951.2092266663799</v>
       </c>
       <c r="K68" s="5">
-        <v>1.27864582846584</v>
+        <v>2.6106597057721299E-2</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>164</v>
-      </c>
-      <c r="B69" t="s">
-        <v>86</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E69" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E69" t="s">
         <v>415</v>
       </c>
-      <c r="F69" t="s">
-        <v>85</v>
+      <c r="G69" t="s">
+        <v>271</v>
       </c>
       <c r="J69" s="5">
-        <v>301995.17204020103</v>
+        <v>40738.027780411299</v>
       </c>
       <c r="K69" s="5">
-        <v>2.67146978214635</v>
+        <v>0.36037135780806401</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>476</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E70" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" t="s">
         <v>415</v>
       </c>
       <c r="F70" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="G70" t="s">
-        <v>442</v>
+        <v>271</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J70">
-        <v>47863.009232263801</v>
+        <v>434</v>
+      </c>
+      <c r="J70" s="5">
+        <v>223872.11385683299</v>
       </c>
       <c r="K70" s="5">
-        <v>0.42339942715893297</v>
+        <v>1.9803879088310199</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>477</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F71" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="G71" t="s">
-        <v>442</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J71">
-        <v>2511.8864315095798</v>
-      </c>
-      <c r="K71">
-        <v>2.22203178038488E-2</v>
+        <v>431</v>
+      </c>
+      <c r="J71" s="5">
+        <v>338844.15613920201</v>
+      </c>
+      <c r="K71" s="5">
+        <v>2.99743839567825</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>158</v>
-      </c>
-      <c r="B72" t="s">
-        <v>49</v>
+        <v>294</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F72" t="s">
-        <v>50</v>
+        <v>414</v>
       </c>
       <c r="G72" t="s">
-        <v>442</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>436</v>
+        <v>271</v>
       </c>
       <c r="J72" s="5">
-        <v>281838.29312644497</v>
+        <v>13803.842646028799</v>
       </c>
       <c r="K72" s="5">
-        <v>2.4931606636372798</v>
+        <v>0.122109728633212</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F73" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G73" t="s">
-        <v>412</v>
-      </c>
-      <c r="H73" t="s">
-        <v>5</v>
+        <v>428</v>
       </c>
       <c r="J73" s="5">
-        <v>245470.891568502</v>
+        <v>91201.083935590897</v>
       </c>
       <c r="K73" s="5">
-        <v>2.1714521619388099</v>
+        <v>0.80677097645948803</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>293</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C74" s="1"/>
+        <v>162</v>
+      </c>
+      <c r="B74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>472</v>
+      </c>
       <c r="D74" s="1" t="s">
-        <v>398</v>
+        <v>257</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
+      </c>
+      <c r="F74" t="s">
+        <v>50</v>
       </c>
       <c r="G74" t="s">
-        <v>499</v>
+        <v>440</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J74" s="5">
-        <v>17378.0082874937</v>
+        <v>53703.1796370253</v>
       </c>
       <c r="K74" s="5">
-        <v>0.15372704040363999</v>
+        <v>0.47506197081320301</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E75" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E75" t="s">
         <v>415</v>
       </c>
       <c r="F75" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
-        <v>434</v>
+        <v>272</v>
       </c>
       <c r="J75" s="5">
-        <v>213796.20895022299</v>
+        <v>144543.977074592</v>
       </c>
       <c r="K75" s="5">
-        <v>1.89125577038012</v>
+        <v>1.27864582846584</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>283</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C76" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="B76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>473</v>
+      </c>
       <c r="D76" s="1" t="s">
-        <v>364</v>
+        <v>184</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" t="s">
-        <v>430</v>
-      </c>
-      <c r="H76" t="s">
-        <v>498</v>
+        <v>414</v>
+      </c>
+      <c r="F76" t="s">
+        <v>85</v>
       </c>
       <c r="J76" s="5">
-        <v>12022.6443461741</v>
+        <v>301995.17204020103</v>
       </c>
       <c r="K76" s="5">
-        <v>0.106353127618945</v>
+        <v>2.67146978214635</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
-      </c>
-      <c r="C77" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="D77" s="1" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F77" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G77" t="s">
-        <v>430</v>
-      </c>
-      <c r="H77" t="s">
-        <v>498</v>
-      </c>
-      <c r="J77" s="5">
-        <v>645654.22903465398</v>
+        <v>440</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J77">
+        <v>47863.009232263801</v>
       </c>
       <c r="K77" s="5">
-        <v>5.7115011174796901</v>
+        <v>0.42339942715893297</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>330</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C78" s="1"/>
+        <v>165</v>
+      </c>
+      <c r="B78" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="D78" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="E78" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E78" t="s">
         <v>415</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="F78" t="s">
         <v>5</v>
       </c>
-      <c r="J78" s="5">
-        <v>812.83051616409898</v>
+      <c r="G78" t="s">
+        <v>440</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J78">
+        <v>2511.8864315095798</v>
       </c>
       <c r="K78">
-        <v>7.1903538962859699E-3</v>
+        <v>2.22203178038488E-2</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>478</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="G79" t="s">
-        <v>271</v>
+        <v>440</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J79" s="5">
-        <v>4265.7951880159198</v>
+        <v>281838.29312644497</v>
       </c>
       <c r="K79" s="5">
-        <v>3.77355136660689E-2</v>
+        <v>2.4931606636372798</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F80" t="s">
         <v>87</v>
       </c>
+      <c r="G80" t="s">
+        <v>411</v>
+      </c>
       <c r="H80" t="s">
-        <v>498</v>
+        <v>5</v>
       </c>
       <c r="J80" s="5">
-        <v>24547.089156850201</v>
+        <v>245470.891568502</v>
       </c>
       <c r="K80" s="5">
-        <v>0.217145216193881</v>
+        <v>2.1714521619388099</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>170</v>
-      </c>
-      <c r="B81" t="s">
-        <v>118</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>479</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>255</v>
+        <v>397</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F81" t="s">
-        <v>85</v>
+        <v>414</v>
+      </c>
+      <c r="G81" t="s">
+        <v>497</v>
       </c>
       <c r="J81" s="5">
-        <v>131825.67385563999</v>
+        <v>17378.0082874937</v>
       </c>
       <c r="K81" s="5">
-        <v>1.16613885525807</v>
+        <v>0.15372704040363999</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>480</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E82" t="s">
-        <v>416</v>
+        <v>217</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F82" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G82" t="s">
-        <v>442</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J82" s="5">
-        <v>26302.6799189538</v>
+        <v>213796.20895022299</v>
       </c>
       <c r="K82" s="5">
-        <v>0.23267529119173699</v>
+        <v>1.89125577038012</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="G83" t="s">
-        <v>442</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
+      </c>
+      <c r="H83" t="s">
+        <v>496</v>
       </c>
       <c r="J83" s="5">
-        <v>234422.881531992</v>
+        <v>12022.6443461741</v>
       </c>
       <c r="K83" s="5">
-        <v>2.0737207155517798</v>
+        <v>0.106353127618945</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F84" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G84" t="s">
-        <v>411</v>
+        <v>428</v>
+      </c>
+      <c r="H84" t="s">
+        <v>496</v>
       </c>
       <c r="J84" s="5">
-        <v>562341.32519034902</v>
+        <v>645654.22903465398</v>
       </c>
       <c r="K84" s="5">
-        <v>4.9745095173182801</v>
+        <v>5.7115011174796901</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>51</v>
-      </c>
-      <c r="B85" t="s">
-        <v>52</v>
+        <v>329</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>207</v>
+        <v>384</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F85" t="s">
+        <v>414</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H85" t="s">
         <v>5</v>
       </c>
       <c r="J85" s="5">
-        <v>41686.938347033501</v>
-      </c>
-      <c r="K85" s="5">
-        <v>0.368765485063692</v>
+        <v>812.83051616409898</v>
+      </c>
+      <c r="K85">
+        <v>7.1903538962859699E-3</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>282</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C86" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="B86" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>476</v>
+      </c>
       <c r="D86" s="1" t="s">
-        <v>363</v>
+        <v>215</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>26</v>
+        <v>414</v>
+      </c>
+      <c r="F86" t="s">
+        <v>95</v>
       </c>
       <c r="G86" t="s">
-        <v>430</v>
-      </c>
-      <c r="H86" t="s">
-        <v>439</v>
+        <v>271</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J86" s="5">
-        <v>6760.8297539198102</v>
-      </c>
-      <c r="K86">
-        <v>5.9806758723376E-2</v>
+        <v>4265.7951880159198</v>
+      </c>
+      <c r="K86" s="5">
+        <v>3.77355136660689E-2</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>53</v>
-      </c>
-      <c r="B87" t="s">
-        <v>54</v>
-      </c>
-      <c r="C87" s="1"/>
+        <v>532</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="D87" s="1" t="s">
-        <v>247</v>
+        <v>535</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F87" t="s">
-        <v>16</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H87" t="s">
-        <v>5</v>
-      </c>
-      <c r="J87" s="5">
-        <v>33113.112148259002</v>
-      </c>
-      <c r="K87" s="5">
-        <v>0.292920836777886</v>
+      <c r="F87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G87" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>424</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s">
-        <v>5</v>
+        <v>496</v>
       </c>
       <c r="J88" s="5">
-        <v>20892.961308540402</v>
+        <v>24547.089156850201</v>
       </c>
       <c r="K88" s="5">
-        <v>0.18482055331629099</v>
+        <v>0.217145216193881</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
-      </c>
-      <c r="C89" s="1"/>
+        <v>118</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="D89" s="1" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H89" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="J89" s="5">
-        <v>208929.61308540401</v>
+        <v>131825.67385563999</v>
       </c>
       <c r="K89" s="5">
-        <v>1.8482055331629099</v>
+        <v>1.16613885525807</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>478</v>
+      </c>
       <c r="D90" s="1" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="E90" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F90" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="G90" t="s">
-        <v>432</v>
-      </c>
-      <c r="J90">
-        <v>36307.805477010101</v>
+        <v>440</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J90" s="5">
+        <v>26302.6799189538</v>
       </c>
       <c r="K90" s="5">
-        <v>0.32118131072296802</v>
+        <v>0.23267529119173699</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>481</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E91" t="s">
-        <v>416</v>
-      </c>
-      <c r="F91" t="s">
-        <v>80</v>
+        <v>396</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="G91" t="s">
-        <v>432</v>
+        <v>440</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J91" s="5">
-        <v>6456.5422903465496</v>
-      </c>
-      <c r="K91">
-        <v>5.7115011174796899E-2</v>
+        <v>234422.881531992</v>
+      </c>
+      <c r="K91" s="5">
+        <v>2.0737207155517798</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>173</v>
-      </c>
-      <c r="B92" t="s">
-        <v>82</v>
+        <v>549</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>546</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>481</v>
+        <v>547</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E92" t="s">
-        <v>416</v>
-      </c>
-      <c r="F92" t="s">
-        <v>80</v>
+        <v>548</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="G92" t="s">
-        <v>432</v>
-      </c>
-      <c r="J92" s="5">
-        <v>6456.5422903465496</v>
-      </c>
-      <c r="K92">
-        <v>5.7115011174796899E-2</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F93" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s">
-        <v>435</v>
-      </c>
-      <c r="H93" t="s">
-        <v>498</v>
+        <v>410</v>
       </c>
       <c r="J93" s="5">
-        <v>138038.426460288</v>
+        <v>562341.32519034902</v>
       </c>
       <c r="K93" s="5">
-        <v>1.2210972863321199</v>
+        <v>4.9745095173182801</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>351</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
+      </c>
+      <c r="B94" t="s">
+        <v>52</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E94" t="s">
-        <v>416</v>
+        <v>207</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F94" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H94" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="J94" s="5">
-        <v>70794.578438413693</v>
+        <v>41686.938347033501</v>
       </c>
       <c r="K94" s="5">
-        <v>0.62625364425639096</v>
+        <v>0.368765485063692</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>59</v>
-      </c>
-      <c r="B95" t="s">
-        <v>60</v>
+        <v>281</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E95" t="s">
-        <v>416</v>
-      </c>
-      <c r="F95" t="s">
-        <v>5</v>
+        <v>362</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G95" t="s">
-        <v>271</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
+      </c>
+      <c r="H95" t="s">
+        <v>437</v>
       </c>
       <c r="J95" s="5">
-        <v>70794.578438413693</v>
-      </c>
-      <c r="K95" s="5">
-        <v>0.62625364425639096</v>
+        <v>6760.8297539198102</v>
+      </c>
+      <c r="K95">
+        <v>5.9806758723376E-2</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>53</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E96" t="s">
-        <v>416</v>
+        <v>247</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" t="s">
-        <v>273</v>
+        <v>16</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H96" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="5">
-        <v>5495.4087385762396</v>
-      </c>
-      <c r="K96">
-        <v>4.8612758563223502E-2</v>
+        <v>33113.112148259002</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0.292920836777886</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>311</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>312</v>
+        <v>55</v>
+      </c>
+      <c r="B97" t="s">
+        <v>56</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1" t="s">
-        <v>375</v>
+        <v>230</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
+      </c>
+      <c r="F97" t="s">
+        <v>16</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="H97" t="s">
-        <v>438</v>
+        <v>5</v>
       </c>
       <c r="J97" s="5">
-        <v>6760.8297539198102</v>
-      </c>
-      <c r="K97">
-        <v>5.9806758723376E-2</v>
+        <v>20892.961308540402</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0.18482055331629099</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F98" t="s">
-        <v>87</v>
-      </c>
-      <c r="G98" t="s">
-        <v>442</v>
+        <v>16</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="H98" t="s">
         <v>5</v>
       </c>
       <c r="J98" s="5">
-        <v>213796.20895022299</v>
+        <v>208929.61308540401</v>
       </c>
       <c r="K98" s="5">
-        <v>1.89125577038012</v>
+        <v>1.8482055331629099</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="B99" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E99" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E99" t="s">
         <v>415</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>135</v>
+      <c r="F99" t="s">
+        <v>80</v>
       </c>
       <c r="G99" t="s">
-        <v>496</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J99" s="5">
-        <v>14454.3977074592</v>
+        <v>430</v>
+      </c>
+      <c r="J99">
+        <v>36307.805477010101</v>
       </c>
       <c r="K99" s="5">
-        <v>0.127864582846584</v>
+        <v>0.32118131072296802</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>143</v>
-      </c>
-      <c r="B100" t="s">
-        <v>84</v>
-      </c>
-      <c r="C100" s="1"/>
+        <v>307</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>479</v>
+      </c>
       <c r="D100" s="1" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="E100" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F100" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s">
-        <v>496</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="J100" s="5">
-        <v>75857.757502918306</v>
-      </c>
-      <c r="K100" s="5">
-        <v>0.67104286979612804</v>
+        <v>6456.5422903465496</v>
+      </c>
+      <c r="K100">
+        <v>5.7115011174796899E-2</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
-      </c>
-      <c r="C101" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>479</v>
+      </c>
       <c r="D101" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E101" t="s">
         <v>415</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H101" t="s">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="G101" t="s">
+        <v>430</v>
       </c>
       <c r="J101" s="5">
-        <v>134896.28825916501</v>
-      </c>
-      <c r="K101" s="5">
-        <v>1.1933017186118799</v>
+        <v>6456.5422903465496</v>
+      </c>
+      <c r="K101">
+        <v>5.7115011174796899E-2</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>345</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>346</v>
+        <v>516</v>
+      </c>
+      <c r="B102" t="s">
+        <v>82</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E102" t="s">
         <v>415</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H102" t="s">
-        <v>496</v>
-      </c>
-      <c r="J102" s="5">
-        <v>4073.8027780411198</v>
-      </c>
-      <c r="K102">
-        <v>3.6037135780806397E-2</v>
-      </c>
+      <c r="F102" t="s">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s">
+        <v>429</v>
+      </c>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F103" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G103" t="s">
-        <v>423</v>
+        <v>433</v>
+      </c>
+      <c r="H103" t="s">
+        <v>496</v>
       </c>
       <c r="J103" s="5">
-        <v>70794.578438413693</v>
+        <v>138038.426460288</v>
       </c>
       <c r="K103" s="5">
-        <v>0.62625364425639096</v>
+        <v>1.2210972863321199</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>178</v>
-      </c>
-      <c r="B104" t="s">
-        <v>89</v>
+        <v>350</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E104" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" t="s">
         <v>415</v>
       </c>
       <c r="F104" t="s">
-        <v>87</v>
-      </c>
-      <c r="G104" t="s">
-        <v>411</v>
-      </c>
-      <c r="H104" t="s">
         <v>5</v>
       </c>
+      <c r="G104" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="J104" s="5">
-        <v>323593.65692962799</v>
+        <v>70794.578438413693</v>
       </c>
       <c r="K104" s="5">
-        <v>2.8625314449287198</v>
+        <v>0.62625364425639096</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E105" t="s">
         <v>415</v>
       </c>
       <c r="F105" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="G105" t="s">
-        <v>442</v>
+        <v>271</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J105" s="5">
-        <v>67608.297539198102</v>
+        <v>70794.578438413693</v>
       </c>
       <c r="K105" s="5">
-        <v>0.59806758723375997</v>
+        <v>0.62625364425639096</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B106" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="E106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F106" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>424</v>
+        <v>272</v>
       </c>
       <c r="J106" s="5">
-        <v>25118.864315095801</v>
-      </c>
-      <c r="K106" s="5">
-        <v>0.22220317803848799</v>
+        <v>5495.4087385762396</v>
+      </c>
+      <c r="K106">
+        <v>4.8612758563223502E-2</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>180</v>
-      </c>
-      <c r="B107" t="s">
-        <v>104</v>
+        <v>310</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E107" t="s">
-        <v>415</v>
-      </c>
-      <c r="F107" t="s">
-        <v>105</v>
-      </c>
-      <c r="G107" t="s">
-        <v>424</v>
-      </c>
-      <c r="J107">
-        <v>47863.009232263801</v>
-      </c>
-      <c r="K107" s="5">
-        <v>0.42339942715893297</v>
+        <v>374</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H107" t="s">
+        <v>436</v>
+      </c>
+      <c r="J107" s="5">
+        <v>6760.8297539198102</v>
+      </c>
+      <c r="K107">
+        <v>5.9806758723376E-2</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="B108" t="s">
-        <v>68</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>483</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C108" s="1"/>
       <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E108" t="s">
-        <v>416</v>
+        <v>205</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="G108" t="s">
-        <v>273</v>
+        <v>440</v>
+      </c>
+      <c r="H108" t="s">
+        <v>5</v>
       </c>
       <c r="J108" s="5">
-        <v>7585.7757502918303</v>
-      </c>
-      <c r="K108">
-        <v>6.7104286979612807E-2</v>
+        <v>213796.20895022299</v>
+      </c>
+      <c r="K108" s="5">
+        <v>1.89125577038012</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>313</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>483</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="B109" t="s">
+        <v>140</v>
+      </c>
+      <c r="C109" s="1"/>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="G109" t="s">
-        <v>274</v>
+        <v>494</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J109" s="5">
-        <v>7585.7757502918303</v>
-      </c>
-      <c r="K109">
-        <v>6.7104286979612807E-2</v>
+        <v>14454.3977074592</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0.127864582846584</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>484</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="E110" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G110" t="s">
-        <v>273</v>
-      </c>
-      <c r="J110">
-        <v>6309.5734448019302</v>
+        <v>494</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J110" s="5">
+        <v>75857.757502918306</v>
       </c>
       <c r="K110" s="5">
-        <v>5.5814914795318603E-2</v>
+        <v>0.67104286979612804</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A111" t="s">
-        <v>173</v>
+      <c r="A111" s="6" t="s">
+        <v>509</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>510</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E111" t="s">
-        <v>416</v>
-      </c>
-      <c r="F111" t="s">
-        <v>80</v>
-      </c>
-      <c r="G111" t="s">
-        <v>272</v>
-      </c>
-      <c r="J111" s="5">
-        <v>107151.93052376001</v>
-      </c>
-      <c r="K111" s="5">
-        <v>0.94787324763842995</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>321</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>322</v>
+        <v>62</v>
+      </c>
+      <c r="B112" t="s">
+        <v>63</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1" t="s">
-        <v>379</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
+      </c>
+      <c r="F112" t="s">
+        <v>16</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="J112">
-        <v>6309.5734448019302</v>
+        <v>422</v>
+      </c>
+      <c r="H112" t="s">
+        <v>5</v>
+      </c>
+      <c r="J112" s="5">
+        <v>134896.28825916501</v>
       </c>
       <c r="K112" s="5">
-        <v>5.5814914795318603E-2</v>
+        <v>1.1933017186118799</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>157</v>
-      </c>
-      <c r="B113" t="s">
-        <v>97</v>
+        <v>344</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>216</v>
+        <v>389</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F113" t="s">
-        <v>95</v>
-      </c>
-      <c r="G113" t="s">
-        <v>271</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>436</v>
+        <v>414</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H113" t="s">
+        <v>494</v>
       </c>
       <c r="J113" s="5">
-        <v>87096.358995608098</v>
+        <v>4073.8027780411198</v>
       </c>
       <c r="K113">
-        <v>0.77046030113608699</v>
+        <v>3.6037135780806397E-2</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E114" t="s">
-        <v>416</v>
+        <v>258</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="G114" t="s">
-        <v>273</v>
+        <v>421</v>
       </c>
       <c r="J114" s="5">
-        <v>81283.051616409895</v>
+        <v>70794.578438413693</v>
       </c>
       <c r="K114" s="5">
-        <v>0.71903538962859703</v>
+        <v>0.62625364425639096</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B115" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F115" t="s">
         <v>87</v>
       </c>
       <c r="G115" t="s">
-        <v>271</v>
+        <v>410</v>
       </c>
       <c r="H115" t="s">
         <v>5</v>
       </c>
       <c r="J115" s="5">
-        <v>194984.459975804</v>
+        <v>323593.65692962799</v>
       </c>
       <c r="K115" s="5">
-        <v>1.72484576258108</v>
+        <v>2.8625314449287198</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>288</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>486</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="B116" t="s">
+        <v>96</v>
+      </c>
+      <c r="C116" s="1"/>
       <c r="D116" s="1" t="s">
-        <v>367</v>
+        <v>252</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>13</v>
+        <v>414</v>
+      </c>
+      <c r="F116" t="s">
+        <v>95</v>
       </c>
       <c r="G116" t="s">
-        <v>273</v>
+        <v>440</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J116" s="5">
-        <v>1071.5193052376001</v>
-      </c>
-      <c r="K116">
-        <v>9.4787324763842898E-3</v>
+        <v>67608.297539198102</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0.59806758723375997</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>323</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>405</v>
+        <v>179</v>
+      </c>
+      <c r="B117" t="s">
+        <v>129</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E117" t="s">
         <v>415</v>
       </c>
-      <c r="G117" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>380</v>
+      <c r="F117" t="s">
+        <v>105</v>
+      </c>
+      <c r="G117" t="s">
+        <v>422</v>
       </c>
       <c r="J117" s="5">
-        <v>28840.315031266</v>
+        <v>25118.864315095801</v>
       </c>
       <c r="K117" s="5">
-        <v>0.25512338357300701</v>
+        <v>0.22220317803848799</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>415</v>
+        <v>231</v>
+      </c>
+      <c r="E118" t="s">
+        <v>414</v>
       </c>
       <c r="F118" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="G118" t="s">
-        <v>411</v>
-      </c>
-      <c r="H118" t="s">
-        <v>5</v>
-      </c>
-      <c r="J118" s="5">
-        <v>41686.938347033501</v>
+        <v>422</v>
+      </c>
+      <c r="J118">
+        <v>47863.009232263801</v>
       </c>
       <c r="K118" s="5">
-        <v>0.368765485063692</v>
+        <v>0.42339942715893297</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>327</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>328</v>
+        <v>67</v>
+      </c>
+      <c r="B119" t="s">
+        <v>68</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E119" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E119" t="s">
         <v>415</v>
       </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
       <c r="G119" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J119" s="5">
-        <v>912.01083935590896</v>
+        <v>7585.7757502918303</v>
       </c>
       <c r="K119">
-        <v>8.0677097645948798E-3</v>
+        <v>6.7104286979612807E-2</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C120" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>481</v>
+      </c>
       <c r="D120" s="1" t="s">
-        <v>365</v>
+        <v>235</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="H120" t="s">
-        <v>439</v>
+        <v>13</v>
+      </c>
+      <c r="G120" t="s">
+        <v>273</v>
       </c>
       <c r="J120" s="5">
-        <v>2630.26799189538</v>
-      </c>
-      <c r="K120" s="5">
-        <v>2.3267529119173701E-2</v>
+        <v>7585.7757502918303</v>
+      </c>
+      <c r="K120">
+        <v>6.7104286979612807E-2</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>277</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>356</v>
+        <v>69</v>
+      </c>
+      <c r="B121" t="s">
+        <v>70</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E121" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E121" t="s">
         <v>415</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>135</v>
+      <c r="F121" t="s">
+        <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>271</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="J121" s="5">
-        <v>2454.7089156850302</v>
+        <v>272</v>
+      </c>
+      <c r="J121">
+        <v>6309.5734448019302</v>
       </c>
       <c r="K121" s="5">
-        <v>2.17145216193881E-2</v>
+        <v>5.5814914795318603E-2</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>343</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>489</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B122" t="s">
+        <v>116</v>
+      </c>
+      <c r="C122" s="1"/>
       <c r="D122" s="1" t="s">
-        <v>389</v>
+        <v>194</v>
       </c>
       <c r="E122" t="s">
-        <v>416</v>
+        <v>415</v>
+      </c>
+      <c r="F122" t="s">
+        <v>80</v>
       </c>
       <c r="G122" t="s">
-        <v>445</v>
-      </c>
-      <c r="J122">
-        <v>9549.92586021436</v>
-      </c>
-      <c r="K122">
-        <v>8.4479292118963101E-2</v>
+        <v>273</v>
+      </c>
+      <c r="J122" s="5">
+        <v>107151.93052376001</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0.94787324763842995</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>182</v>
-      </c>
-      <c r="B123" t="s">
-        <v>131</v>
+        <v>320</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1" t="s">
-        <v>268</v>
+        <v>378</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F123" t="s">
-        <v>107</v>
-      </c>
-      <c r="G123" t="s">
-        <v>411</v>
-      </c>
-      <c r="J123" s="5">
-        <v>26302.6799189538</v>
+        <v>414</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J123">
+        <v>6309.5734448019302</v>
       </c>
       <c r="K123" s="5">
-        <v>0.23267529119173699</v>
+        <v>5.5814914795318603E-2</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>291</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>292</v>
+        <v>157</v>
+      </c>
+      <c r="B124" t="s">
+        <v>97</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E124" t="s">
-        <v>416</v>
+        <v>216</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F124" t="s">
+        <v>95</v>
       </c>
       <c r="G124" t="s">
-        <v>273</v>
+        <v>271</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="J124" s="5">
-        <v>54954.087385762403</v>
-      </c>
-      <c r="K124" s="5">
-        <v>0.48612758563223502</v>
+        <v>87096.358995608098</v>
+      </c>
+      <c r="K124">
+        <v>0.77046030113608699</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>349</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>493</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B125" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" s="1"/>
       <c r="D125" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E125" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E125" t="s">
         <v>415</v>
       </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" t="s">
+        <v>272</v>
+      </c>
       <c r="J125" s="5">
-        <v>13489.628825916499</v>
+        <v>81283.051616409895</v>
       </c>
       <c r="K125" s="5">
-        <v>0.11933017186118799</v>
+        <v>0.71903538962859703</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>418</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>494</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B126" t="s">
+        <v>101</v>
+      </c>
+      <c r="C126" s="1"/>
       <c r="D126" s="1" t="s">
-        <v>403</v>
+        <v>221</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G126" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F126" t="s">
+        <v>87</v>
+      </c>
+      <c r="G126" t="s">
         <v>271</v>
       </c>
+      <c r="H126" t="s">
+        <v>5</v>
+      </c>
       <c r="J126" s="5">
-        <v>239883.29190194799</v>
+        <v>194984.459975804</v>
       </c>
       <c r="K126" s="5">
-        <v>2.12202387617157</v>
+        <v>1.72484576258108</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C127" s="1"/>
+        <v>288</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>484</v>
+      </c>
       <c r="D127" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E127" t="s">
-        <v>416</v>
+        <v>366</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>445</v>
+        <v>272</v>
       </c>
       <c r="J127" s="5">
-        <v>7943.2823472428099</v>
+        <v>1071.5193052376001</v>
       </c>
       <c r="K127">
-        <v>7.0266814592952795E-2</v>
+        <v>9.4787324763842898E-3</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>87</v>
+        <v>414</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="H128" t="s">
-        <v>5</v>
+        <v>444</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="J128" s="5">
-        <v>33113.112148259002</v>
+        <v>28840.315031266</v>
       </c>
       <c r="K128" s="5">
-        <v>0.292920836777886</v>
+        <v>0.25512338357300701</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>490</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C129" s="1"/>
       <c r="D129" s="1" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F129" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="G129" t="s">
-        <v>271</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>436</v>
+        <v>410</v>
+      </c>
+      <c r="H129" t="s">
+        <v>5</v>
       </c>
       <c r="J129" s="5">
-        <v>1698.2436524617401</v>
-      </c>
-      <c r="K129">
-        <v>1.50227785749815E-2</v>
+        <v>41686.938347033501</v>
+      </c>
+      <c r="K129" s="5">
+        <v>0.368765485063692</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C130" s="1"/>
+        <v>327</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>485</v>
+      </c>
       <c r="D130" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E130" t="s">
-        <v>416</v>
+        <v>382</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="G130" t="s">
-        <v>411</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>382</v>
+        <v>271</v>
       </c>
       <c r="J130" s="5">
-        <v>45708.818961487501</v>
-      </c>
-      <c r="K130" s="5">
-        <v>0.40434331386250399</v>
+        <v>912.01083935590896</v>
+      </c>
+      <c r="K130">
+        <v>8.0677097645948798E-3</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G131" t="s">
-        <v>411</v>
+        <v>414</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H131" t="s">
+        <v>437</v>
       </c>
       <c r="J131" s="5">
-        <v>45708.818961487501</v>
+        <v>2630.26799189538</v>
       </c>
       <c r="K131" s="5">
-        <v>0.40434331386250399</v>
+        <v>2.3267529119173701E-2</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C132" s="1"/>
+        <v>355</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>486</v>
+      </c>
       <c r="D132" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="E132" t="s">
-        <v>416</v>
+        <v>359</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="G132" t="s">
-        <v>419</v>
-      </c>
-      <c r="H132" t="s">
         <v>271</v>
       </c>
-      <c r="I132" t="s">
-        <v>425</v>
+      <c r="H132" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="J132" s="5">
-        <v>34673.6850452531</v>
+        <v>2454.7089156850302</v>
       </c>
       <c r="K132" s="5">
-        <v>0.30672577050908201</v>
+        <v>2.17145216193881E-2</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>426</v>
+        <v>342</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C133" s="1"/>
+        <v>343</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>487</v>
+      </c>
       <c r="D133" s="1" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="E133" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G133" t="s">
-        <v>411</v>
-      </c>
-      <c r="J133" s="5">
-        <v>34673.6850452531</v>
-      </c>
-      <c r="K133" s="5">
-        <v>0.30672577050908201</v>
+        <v>443</v>
+      </c>
+      <c r="J133">
+        <v>9549.92586021436</v>
+      </c>
+      <c r="K133">
+        <v>8.4479292118963101E-2</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>280</v>
+        <v>521</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C134" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>522</v>
+      </c>
       <c r="D134" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E134" t="s">
-        <v>416</v>
+        <v>268</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="G134" t="s">
-        <v>411</v>
-      </c>
-      <c r="J134" s="5">
-        <v>34673.6850452531</v>
-      </c>
-      <c r="K134" s="5">
-        <v>0.30672577050908201</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="J134" s="5"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>329</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>281</v>
+        <v>182</v>
+      </c>
+      <c r="B135" t="s">
+        <v>131</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E135" t="s">
-        <v>416</v>
+        <v>268</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F135" t="s">
+        <v>107</v>
       </c>
       <c r="G135" t="s">
-        <v>411</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="J135" s="5">
-        <v>34673.6850452531</v>
+        <v>26302.6799189538</v>
       </c>
       <c r="K135" s="5">
-        <v>0.30672577050908201</v>
+        <v>0.23267529119173699</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C136" s="1"/>
+        <v>291</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>490</v>
+      </c>
       <c r="D136" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E136" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G136" t="s">
-        <v>411</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>384</v>
+        <v>272</v>
       </c>
       <c r="J136" s="5">
-        <v>34673.6850452531</v>
+        <v>54954.087385762403</v>
       </c>
       <c r="K136" s="5">
-        <v>0.30672577050908201</v>
+        <v>0.48612758563223502</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>73</v>
-      </c>
-      <c r="B137" t="s">
-        <v>74</v>
+        <v>348</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>245</v>
+        <v>391</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F137" t="s">
-        <v>16</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="H137" t="s">
-        <v>5</v>
+        <v>414</v>
       </c>
       <c r="J137" s="5">
-        <v>323593.65692962799</v>
+        <v>13489.628825916499</v>
       </c>
       <c r="K137" s="5">
-        <v>2.8625314449287198</v>
+        <v>0.11933017186118799</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>155</v>
-      </c>
-      <c r="B138" t="s">
-        <v>98</v>
+        <v>417</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>253</v>
+        <v>402</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F138" t="s">
-        <v>95</v>
-      </c>
-      <c r="G138" t="s">
+        <v>414</v>
+      </c>
+      <c r="G138" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H138" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="J138" s="5">
-        <v>32359.365692962801</v>
+        <v>239883.29190194799</v>
       </c>
       <c r="K138" s="5">
-        <v>0.28625314449287198</v>
+        <v>2.12202387617157</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
+        <v>339</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E139" t="s">
+        <v>415</v>
+      </c>
+      <c r="G139" t="s">
+        <v>443</v>
+      </c>
+      <c r="J139" s="5">
+        <v>7943.2823472428099</v>
+      </c>
+      <c r="K139">
+        <v>7.0266814592952795E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A140" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B140" t="s">
+        <v>347</v>
+      </c>
+      <c r="C140" t="s">
+        <v>507</v>
+      </c>
+      <c r="D140" t="s">
+        <v>390</v>
+      </c>
+      <c r="E140" t="s">
+        <v>414</v>
+      </c>
+      <c r="F140" t="s">
+        <v>87</v>
+      </c>
+      <c r="G140" t="s">
+        <v>271</v>
+      </c>
+      <c r="J140" s="5"/>
+      <c r="K140" s="5"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>346</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H141" t="s">
+        <v>5</v>
+      </c>
+      <c r="J141" s="5">
+        <v>33113.112148259002</v>
+      </c>
+      <c r="K141" s="5">
+        <v>0.292920836777886</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>183</v>
+      </c>
+      <c r="B142" t="s">
+        <v>121</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F142" t="s">
+        <v>50</v>
+      </c>
+      <c r="G142" t="s">
+        <v>271</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J142" s="5">
+        <v>1698.2436524617401</v>
+      </c>
+      <c r="K142">
+        <v>1.50227785749815E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>324</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E143" t="s">
+        <v>415</v>
+      </c>
+      <c r="G143" t="s">
+        <v>410</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J143" s="5">
+        <v>45708.818961487501</v>
+      </c>
+      <c r="K143" s="5">
+        <v>0.40434331386250399</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>315</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G144" t="s">
+        <v>410</v>
+      </c>
+      <c r="J144" s="5">
+        <v>45708.818961487501</v>
+      </c>
+      <c r="K144" s="5">
+        <v>0.40434331386250399</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E145" t="s">
+        <v>415</v>
+      </c>
+      <c r="G145" t="s">
+        <v>410</v>
+      </c>
+      <c r="J145" s="5">
+        <v>34673.6850452531</v>
+      </c>
+      <c r="K145" s="5">
+        <v>0.30672577050908201</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>297</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E146" t="s">
+        <v>415</v>
+      </c>
+      <c r="G146" t="s">
+        <v>418</v>
+      </c>
+      <c r="H146" t="s">
+        <v>271</v>
+      </c>
+      <c r="I146" t="s">
+        <v>423</v>
+      </c>
+      <c r="J146" s="5">
+        <v>34673.6850452531</v>
+      </c>
+      <c r="K146" s="5">
+        <v>0.30672577050908201</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E147" t="s">
+        <v>415</v>
+      </c>
+      <c r="G147" t="s">
+        <v>410</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J147" s="5">
+        <v>34673.6850452531</v>
+      </c>
+      <c r="K147" s="5">
+        <v>0.30672577050908201</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>424</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E148" t="s">
+        <v>415</v>
+      </c>
+      <c r="G148" t="s">
+        <v>410</v>
+      </c>
+      <c r="J148" s="5">
+        <v>34673.6850452531</v>
+      </c>
+      <c r="K148" s="5">
+        <v>0.30672577050908201</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>338</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E149" t="s">
+        <v>415</v>
+      </c>
+      <c r="G149" t="s">
+        <v>410</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J149" s="5">
+        <v>34673.6850452531</v>
+      </c>
+      <c r="K149" s="5">
+        <v>0.30672577050908201</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>73</v>
+      </c>
+      <c r="B150" t="s">
+        <v>74</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F150" t="s">
+        <v>16</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H150" t="s">
+        <v>5</v>
+      </c>
+      <c r="J150" s="5">
+        <v>323593.65692962799</v>
+      </c>
+      <c r="K150" s="5">
+        <v>2.8625314449287198</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>155</v>
+      </c>
+      <c r="B151" t="s">
+        <v>98</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F151" t="s">
+        <v>95</v>
+      </c>
+      <c r="G151" t="s">
+        <v>271</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J151" s="5">
+        <v>32359.365692962801</v>
+      </c>
+      <c r="K151" s="5">
+        <v>0.28625314449287198</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
         <v>75</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B152" t="s">
         <v>76</v>
       </c>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1" t="s">
+      <c r="C152" s="1"/>
+      <c r="D152" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F139" t="s">
+      <c r="E152" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F152" t="s">
         <v>16</v>
       </c>
-      <c r="G139" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="H139" t="s">
+      <c r="G152" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H152" t="s">
         <v>5</v>
       </c>
-      <c r="J139" s="5">
+      <c r="J152" s="5">
         <v>48977.881936844598</v>
       </c>
-      <c r="K139" s="5">
+      <c r="K152" s="5">
         <v>0.433261666747422</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A140" t="s">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
         <v>166</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B153" t="s">
         <v>77</v>
       </c>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1" t="s">
+      <c r="C153" s="1"/>
+      <c r="D153" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="E153" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F153" t="s">
         <v>79</v>
       </c>
-      <c r="G140" t="s">
-        <v>447</v>
-      </c>
-      <c r="J140" s="5">
+      <c r="G153" t="s">
+        <v>445</v>
+      </c>
+      <c r="J153" s="5">
         <v>269153.48039269098</v>
       </c>
-      <c r="K140" s="5">
+      <c r="K153" s="5">
         <v>2.3809499495338899</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K140" xr:uid="{11844E47-879C-4E47-A038-CD7309E4AAED}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K140">
-      <sortCondition ref="B1:B140"/>
+  <autoFilter ref="A1:K150" xr:uid="{11844E47-879C-4E47-A038-CD7309E4AAED}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K153">
+      <sortCondition ref="B1:B150"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8276,10 +8725,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
@@ -8316,7 +8765,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -8460,7 +8909,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B24">
         <v>25</v>
@@ -8468,7 +8917,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B25">
         <v>139</v>
